--- a/project/outputs_xlsx_solution/test_new3.4-wide-NF-1.xlsx
+++ b/project/outputs_xlsx_solution/test_new3.4-wide-NF-1.xlsx
@@ -699,9 +699,6 @@
       <c r="BH1">
         <v>57</v>
       </c>
-      <c r="BI1">
-        <v>58</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1108,12 +1105,9 @@
         <v>6</v>
       </c>
       <c r="T16" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="U16" t="s">
-        <v>8</v>
-      </c>
-      <c r="V16" t="s">
         <v>10</v>
       </c>
       <c r="X16" t="s">
@@ -1137,12 +1131,9 @@
         <v>6</v>
       </c>
       <c r="U17" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V17" t="s">
-        <v>8</v>
-      </c>
-      <c r="W17" t="s">
         <v>10</v>
       </c>
       <c r="X17" t="s">
@@ -1159,11 +1150,14 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
+      <c r="V18" t="s">
+        <v>5</v>
+      </c>
       <c r="W18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="s">
         <v>8</v>
@@ -1172,9 +1166,6 @@
         <v>8</v>
       </c>
       <c r="AA18" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB18" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1188,11 +1179,14 @@
       <c r="C19" t="s">
         <v>16</v>
       </c>
+      <c r="W19" t="s">
+        <v>5</v>
+      </c>
       <c r="X19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="s">
         <v>8</v>
@@ -1204,9 +1198,6 @@
         <v>8</v>
       </c>
       <c r="AC19" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD19" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1220,22 +1211,22 @@
       <c r="C20" t="s">
         <v>20</v>
       </c>
+      <c r="X20" t="s">
+        <v>5</v>
+      </c>
       <c r="Y20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AB20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD20" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1249,19 +1240,19 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
+      <c r="Y21" t="s">
+        <v>5</v>
+      </c>
       <c r="Z21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD21" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1275,16 +1266,16 @@
       <c r="C22" t="s">
         <v>22</v>
       </c>
+      <c r="Z22" t="s">
+        <v>5</v>
+      </c>
       <c r="AA22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1298,16 +1289,16 @@
       <c r="C23" t="s">
         <v>23</v>
       </c>
+      <c r="AA23" t="s">
+        <v>5</v>
+      </c>
       <c r="AB23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE23" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1321,16 +1312,16 @@
       <c r="C24" t="s">
         <v>24</v>
       </c>
+      <c r="AB24" t="s">
+        <v>5</v>
+      </c>
       <c r="AC24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF24" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1344,11 +1335,14 @@
       <c r="C25" t="s">
         <v>19</v>
       </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AD25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="s">
         <v>8</v>
@@ -1357,9 +1351,6 @@
         <v>8</v>
       </c>
       <c r="AH25" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI25" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1373,11 +1364,14 @@
       <c r="C26" t="s">
         <v>16</v>
       </c>
+      <c r="AD26" t="s">
+        <v>5</v>
+      </c>
       <c r="AE26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="s">
         <v>8</v>
@@ -1389,9 +1383,6 @@
         <v>8</v>
       </c>
       <c r="AJ26" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK26" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1405,22 +1396,22 @@
       <c r="C27" t="s">
         <v>20</v>
       </c>
+      <c r="AE27" t="s">
+        <v>5</v>
+      </c>
       <c r="AF27" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG27" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AH27" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AI27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ27" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK27" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1434,19 +1425,19 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
+      <c r="AF28" t="s">
+        <v>5</v>
+      </c>
       <c r="AG28" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK28" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1460,16 +1451,16 @@
       <c r="C29" t="s">
         <v>22</v>
       </c>
+      <c r="AG29" t="s">
+        <v>5</v>
+      </c>
       <c r="AH29" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ29" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK29" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1483,16 +1474,16 @@
       <c r="C30" t="s">
         <v>23</v>
       </c>
+      <c r="AH30" t="s">
+        <v>5</v>
+      </c>
       <c r="AI30" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ30" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="s">
-        <v>8</v>
-      </c>
-      <c r="AL30" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1506,16 +1497,16 @@
       <c r="C31" t="s">
         <v>24</v>
       </c>
+      <c r="AI31" t="s">
+        <v>5</v>
+      </c>
       <c r="AJ31" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AM31" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1529,11 +1520,14 @@
       <c r="C32" t="s">
         <v>19</v>
       </c>
+      <c r="AJ32" t="s">
+        <v>5</v>
+      </c>
       <c r="AK32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL32" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM32" t="s">
         <v>8</v>
@@ -1542,9 +1536,6 @@
         <v>8</v>
       </c>
       <c r="AO32" t="s">
-        <v>8</v>
-      </c>
-      <c r="AP32" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1558,11 +1549,14 @@
       <c r="C33" t="s">
         <v>16</v>
       </c>
+      <c r="AK33" t="s">
+        <v>5</v>
+      </c>
       <c r="AL33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN33" t="s">
         <v>8</v>
@@ -1574,9 +1568,6 @@
         <v>8</v>
       </c>
       <c r="AQ33" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR33" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1590,22 +1581,22 @@
       <c r="C34" t="s">
         <v>20</v>
       </c>
+      <c r="AL34" t="s">
+        <v>5</v>
+      </c>
       <c r="AM34" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN34" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AO34" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AP34" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ34" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR34" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1619,19 +1610,19 @@
       <c r="C35" t="s">
         <v>21</v>
       </c>
+      <c r="AM35" t="s">
+        <v>5</v>
+      </c>
       <c r="AN35" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ35" t="s">
-        <v>10</v>
-      </c>
-      <c r="AR35" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1645,16 +1636,16 @@
       <c r="C36" t="s">
         <v>22</v>
       </c>
+      <c r="AN36" t="s">
+        <v>5</v>
+      </c>
       <c r="AO36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ36" t="s">
-        <v>8</v>
-      </c>
-      <c r="AR36" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1668,16 +1659,16 @@
       <c r="C37" t="s">
         <v>23</v>
       </c>
+      <c r="AO37" t="s">
+        <v>5</v>
+      </c>
       <c r="AP37" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR37" t="s">
-        <v>8</v>
-      </c>
-      <c r="AS37" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1691,16 +1682,16 @@
       <c r="C38" t="s">
         <v>24</v>
       </c>
+      <c r="AP38" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ38" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS38" t="s">
-        <v>8</v>
-      </c>
-      <c r="AT38" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1714,11 +1705,14 @@
       <c r="C39" t="s">
         <v>19</v>
       </c>
+      <c r="AQ39" t="s">
+        <v>5</v>
+      </c>
       <c r="AR39" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT39" t="s">
         <v>8</v>
@@ -1727,9 +1721,6 @@
         <v>8</v>
       </c>
       <c r="AV39" t="s">
-        <v>8</v>
-      </c>
-      <c r="AW39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1743,11 +1734,14 @@
       <c r="C40" t="s">
         <v>16</v>
       </c>
+      <c r="AR40" t="s">
+        <v>5</v>
+      </c>
       <c r="AS40" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT40" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU40" t="s">
         <v>8</v>
@@ -1759,9 +1753,6 @@
         <v>8</v>
       </c>
       <c r="AX40" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY40" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1775,22 +1766,22 @@
       <c r="C41" t="s">
         <v>20</v>
       </c>
+      <c r="AS41" t="s">
+        <v>5</v>
+      </c>
       <c r="AT41" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU41" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AV41" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AW41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX41" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY41" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1804,19 +1795,19 @@
       <c r="C42" t="s">
         <v>21</v>
       </c>
+      <c r="AT42" t="s">
+        <v>5</v>
+      </c>
       <c r="AU42" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV42" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW42" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AY42" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1830,16 +1821,16 @@
       <c r="C43" t="s">
         <v>22</v>
       </c>
+      <c r="AU43" t="s">
+        <v>5</v>
+      </c>
       <c r="AV43" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW43" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="s">
-        <v>8</v>
-      </c>
-      <c r="AY43" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1853,16 +1844,16 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
+      <c r="AV44" t="s">
+        <v>5</v>
+      </c>
       <c r="AW44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX44" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY44" t="s">
-        <v>8</v>
-      </c>
-      <c r="AZ44" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1876,16 +1867,16 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
+      <c r="AW45" t="s">
+        <v>5</v>
+      </c>
       <c r="AX45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY45" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ45" t="s">
-        <v>8</v>
-      </c>
-      <c r="BA45" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1899,11 +1890,14 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
+      <c r="AZ46" t="s">
+        <v>5</v>
+      </c>
       <c r="BA46" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB46" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC46" t="s">
         <v>8</v>
@@ -1912,9 +1906,6 @@
         <v>8</v>
       </c>
       <c r="BE46" t="s">
-        <v>8</v>
-      </c>
-      <c r="BF46" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1928,11 +1919,14 @@
       <c r="C47" t="s">
         <v>16</v>
       </c>
+      <c r="BA47" t="s">
+        <v>5</v>
+      </c>
       <c r="BB47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC47" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD47" t="s">
         <v>8</v>
@@ -1944,9 +1938,6 @@
         <v>8</v>
       </c>
       <c r="BG47" t="s">
-        <v>8</v>
-      </c>
-      <c r="BH47" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1960,22 +1951,22 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
+      <c r="BB48" t="s">
+        <v>5</v>
+      </c>
       <c r="BC48" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD48" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="BE48" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="BF48" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG48" t="s">
-        <v>10</v>
-      </c>
-      <c r="BH48" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1989,19 +1980,19 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
+      <c r="BC49" t="s">
+        <v>5</v>
+      </c>
       <c r="BD49" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE49" t="s">
-        <v>6</v>
-      </c>
-      <c r="BF49" t="s">
         <v>18</v>
       </c>
+      <c r="BG49" t="s">
+        <v>8</v>
+      </c>
       <c r="BH49" t="s">
-        <v>8</v>
-      </c>
-      <c r="BI49" t="s">
         <v>11</v>
       </c>
     </row>
